--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto_Fiets.xlsx
@@ -7276,7 +7276,7 @@
         <v>0.420634026812747</v>
       </c>
       <c r="D407">
-        <v>0.5263226400610853</v>
+        <v>0.5263226400610854</v>
       </c>
       <c r="E407">
         <v>0.6978397746636941</v>
@@ -7372,7 +7372,7 @@
         <v>412</v>
       </c>
       <c r="B413">
-        <v>0.9001951740026319</v>
+        <v>0.9001951740026317</v>
       </c>
       <c r="C413">
         <v>0.8319549355483077</v>
